--- a/BWI/bestwine_output/bestwine_Liechtenstein.xlsx
+++ b/BWI/bestwine_output/bestwine_Liechtenstein.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2274,6 +2274,224 @@
       <c r="Z17" s="4" t="inlineStr"/>
       <c r="AA17" s="4" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Ritter Weine Ag</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Ritter Weine Ag</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>9436</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Schaan</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Schaan</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>23 Poststrasse</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>9494</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ritter-weine.li</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>weine@ritter-weine.li</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>+423 232 17 03</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>CHE-195.571.170</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ritter-weine-ag/</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ritter-weine-119966018065974/</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ritter_weine/</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Michael Gätzi</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michael-g%C3%A4tzi-11b6a61a3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Ritter Weine Ag</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Ritter Weine Ag</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>9436</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Schaan</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Schaan</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>23 Poststrasse</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>9494</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ritter-weine.li</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>weine@ritter-weine.li</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>+423 232 17 03</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>CHE-195.571.170</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ritter-weine-ag/</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ritter-weine-119966018065974/</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ritter_weine/</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>Stephan Ritter</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director &amp; Owner</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stephan-ritter-bbb345246/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Liechtenstein.xlsx
+++ b/BWI/bestwine_output/bestwine_Liechtenstein.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2492,6 +2492,192 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Melanie Gebhart Gebhart's Provinum</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Melanie Gebhart Gebhart's Provinum</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>52962</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Schellenberg</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Schellenberg</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>12 Gutacker</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>9488</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gebharts-provinum.li</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>melanie@gebharts-provinum.li</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>CHE-319.495.332</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GEBHARTs-provinum-245021702351292/</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gebhartsprovinum</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>Melanie Gebhart</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Melanie Gebhart Gebhart's Provinum</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Melanie Gebhart Gebhart's Provinum</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>52962</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Schellenberg</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Schellenberg</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>12 Gutacker</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>9488</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://gebharts-provinum.li</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>melanie@gebharts-provinum.li</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>CHE-319.495.332</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GEBHARTs-provinum-245021702351292/</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gebhartsprovinum</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>Frank Gebhart</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
